--- a/event_planner_forms/003_girl_scout_event_evaluation_form--event_planner_forms.xlsx
+++ b/event_planner_forms/003_girl_scout_event_evaluation_form--event_planner_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event Title</t>
+          <t>Event 2 Title</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event Held On</t>
+          <t>Event 2 Held On</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Event 2 Location</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Number of Scouts Attended</t>
+          <t>Event 2 Scouts Attended</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Number of Scout Leaders Attended</t>
+          <t>Event 2 Scout Leaders Attended</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Risk Assessment Score</t>
+          <t>Event 2 Risk Assessment Score</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Safety Measures Taken</t>
+          <t>Event 2 Safety Measures Taken</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency Contact Info</t>
+          <t>Event 2 Emergency Contact Info</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Number of Scouts Participated</t>
+          <t>Event 2 Scouts Participated</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Number of Scout Leaders Participated</t>
+          <t>Event 2 Scout Leaders Participated</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Event Comments</t>
+          <t>Event 2 Event Comments</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Event Title</t>
+          <t>Event 3 Title</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Event Held On</t>
+          <t>Event 3 Held On</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Event 3 Location</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Safety Measures Taken</t>
+          <t>Event 3 Safety Measures Taken</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency Contact Info</t>
+          <t>Event 3 Emergency Contact Info</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Number of Scouts Participated</t>
+          <t>Event 3 Scouts Participated</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Number of Scout Leaders Participated</t>
+          <t>Event 3 Scout Leaders Participated</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Event Comments</t>
+          <t>Event 3 Event Comments</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
